--- a/reports/集团总公司_利润表_2026-02.xlsx
+++ b/reports/集团总公司_利润表_2026-02.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>198901837</v>
+        <v>216144648</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>151573438</v>
+        <v>163690873</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>302485446</v>
+        <v>327391093</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>617875</v>
+        <v>800836</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1233610</v>
+        <v>1599716</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>534555</v>
+        <v>700886</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>1068244</v>
+        <v>1400948</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>452174</v>
+        <v>591371</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>906119</v>
+        <v>1182878</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>417420</v>
+        <v>545257</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>834954</v>
+        <v>1091397</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>227024</v>
+        <v>299381</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>453141</v>
+        <v>599594</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>180954</v>
+        <v>235478</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>362101</v>
+        <v>471756</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>196471835</v>
+        <v>212971439</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>149143436</v>
+        <v>160517664</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>76596122</v>
+        <v>83509705</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>153162922</v>
+        <v>167341185</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1403019</v>
+        <v>2485129</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>2808619</v>
+        <v>4969081</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1269345</v>
+        <v>1808081</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>2541113</v>
+        <v>3613453</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>68355542</v>
+        <v>71551968</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>136082367</v>
+        <v>142815890</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1447367</v>
+        <v>1815262</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>2893408</v>
+        <v>3623304</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>632715</v>
+        <v>908948</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>1269072</v>
+        <v>1814786</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2273752</v>
+        <v>2731672</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>4543598</v>
+        <v>5454683</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>998595</v>
+        <v>1365237</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>1992966</v>
+        <v>2727792</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>47159677</v>
+        <v>47469136</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>94557920</v>
+        <v>95106385</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>168722</v>
+        <v>175448</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>338376</v>
+        <v>351233</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2887497</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>5781480</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1921694</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>3849399</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>143884352</v>
+        <v>162370273</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>115464368</v>
+        <v>121288947</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>90996048</v>
+        <v>96781947</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>181553283</v>
+        <v>193910322</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>24468320</v>
+        <v>24507000</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>48975176</v>
+        <v>48940142</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>4786455</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>9571198</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1533490</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>3064313</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>959986</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>1917274</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1154017</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>2304128</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>866895</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>1730877</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>578596</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1155600</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>482406</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>964012</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>2664209</v>
+        <v>2682960</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>5347070</v>
+        <v>5367345</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1262283</v>
+        <v>1265862</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>2523863</v>
+        <v>2531563</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>3273707</v>
+        <v>3257794</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>6521145</v>
+        <v>6527632</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>21031630</v>
+        <v>21059672</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>42137715</v>
+        <v>42191607</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>335440</v>
+        <v>2569646</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>672146</v>
+        <v>5145077</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1114998</v>
+        <v>1149409</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>2224347</v>
+        <v>2301788</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1145537</v>
+        <v>1098809</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>2286533</v>
+        <v>2199757</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>116991</v>
+        <v>123077</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>234636</v>
+        <v>246301</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>489585</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>978900</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>838792</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>1675987</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>327345</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>653734</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>245941</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>491042</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>410538</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>819715</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1205538</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>2407907</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>219278</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>438231</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>164405</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>328796</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>273732</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>547830</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>191322</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>383127</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>136419</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>273285</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>108952</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>218280</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>81607</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>163459</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>52587483</v>
+        <v>53683502</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>57053827</v>
+        <v>57092649</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>478771</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>957186</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>136196</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>272110</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>205609</v>
+        <v>216220</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>412366</v>
+        <v>431792</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>52381874</v>
+        <v>53946053</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>6991745</v>
+        <v>7333253</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>13939961</v>
+        <v>14641843</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>45390129</v>
+        <v>46612800</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>45390129</v>
+        <v>46612800</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>45390129</v>
+        <v>46612800</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>45390129</v>
+        <v>46612800</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>45390129</v>
+        <v>46612800</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
